--- a/data/trans_camb/IP16A98-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A98-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.6519315274560428</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.240310474622321</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.101353571249566</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.273852372914691</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.845516934856166</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.239852442868669</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-2.696282662309919</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.822284352881022</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5850154300785771</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.5869533655771945</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.1115131807957224</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-0.5778535918689603</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.663823172418556</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.542984952831889</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.119555642188593</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.003375810823698</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.934080721316564</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5.863542941947395</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.136117351152029</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.2589655037400988</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1.28355162225567</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1.354943390923059</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.5081085126188193</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.6166771335101985</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.4237529792548863</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5035697521172587</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.02933298742460763</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3451692174969922</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.04069150220511487</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1770618992789693</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.200603044531946</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1.968274233243062</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4.808089914878765</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5.696814867227014</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.500722394457046</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.978745315955856</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.1101423862940553</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.722559703157609</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.995090340646804</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.642522936430176</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.9428627134688599</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.690830331890428</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-1.907078864001136</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.64613770881349</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.938028248294373</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.627744293866447</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.611173064955689</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.2897093645829028</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.700811975053636</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.48280091736761</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1211349535877675</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.033057106155145</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.6455933458573785</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.119240277146291</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.06114742009363174</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2.066642367679381</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.5603486778650788</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.4613252528170375</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3515871290598565</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.003392432070952</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.7691426505948789</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.04311872856909651</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.8958619752814403</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.4021558177947347</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7282599266866481</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>6.654154079222983e-05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>3.699960227730002</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11.84110049146207</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.2773051416662176</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.114323540872415</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4514600481354566</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.453780401180649</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.021000303515361</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1052636450735743</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.235798866893238</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.399610923992533</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.5902745973527808</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.265780328910178</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-4.148831269259717</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.175581739509287</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4509192058432946</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.5723141179232392</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.173331690306306</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.7457521217766879</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.031889077567363</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.361436293621138</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.791590354283897</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.868221411575501</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.419191337174408</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.370836665161796</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.3008708570794021</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.03101934740229174</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>5.307621010059527</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>5.696498707796908</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.3062431165535642</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.6567053953127776</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,20 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.8345419230360208</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.6648567394727176</v>
+      </c>
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="n">
+        <v>-0.4872239793387573</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3160598942286287</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1046,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>1.182244183373045</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.836636757432974</v>
+      </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>2.431868978933474</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>3.303062810944688</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1072,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.289567069952356</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.7560048231934569</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-4.106679376363357</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.06273045291963902</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.989852662504985</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.4256583128610852</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1098,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-3.888529725520066</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.543944671497113</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.181542111126063</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.388172833301558</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.660774461932594</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-2.535676034158176</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1124,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.693597133580062</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.232879144862784</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-1.563930290535378</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.837452244772106</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.228448504288643</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.830806032863767</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1150,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.1276927804822575</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.3333816857954658</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.01527522535133716</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.6419003373357547</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.1373117818036512</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1018,14 +1177,19 @@
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="n">
+        <v>-0.7202747423196709</v>
+      </c>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>-0.7385276873069235</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.5336153245060271</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1037,12 +1201,15 @@
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="n">
+        <v>2.891957267437792</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.4632730318803294</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.96738995291233</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1222,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>0.1436025732040096</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.130988823418651</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.5868124873861864</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1.719539638455784</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.3611303216980215</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.42109656372915</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1248,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.551894585729511</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.8008589905272975</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.7506887105801667</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.1038747577612851</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.6764843901967098</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.07645776666414243</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1274,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.663758582117622</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.349737241448118</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.052554237394614</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>3.301954257954649</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1.492932949866232</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>2.891272397320451</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1300,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.04422212605018091</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.3482857527873945</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.2318731455486615</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.6794590664563567</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.124645651438618</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.4904974639358063</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1326,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.3825339060264278</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2216357518042558</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2707458379294741</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.02423251143265298</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.1978011865564827</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.01501566117376664</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1352,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.6552006923096733</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.369541589598966</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1.116200370362218</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.775693455567264</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.619063289542284</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1.140630655050885</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1380,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
